--- a/experiment_results/wedos_grid/rtt_bursts_S1_atk10pct_wu400000_stage1a_rep1.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S1_atk10pct_wu400000_stage1a_rep1.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>84139</t>
+          <t>56849</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>139642</t>
+          <t>82974</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>174417</t>
+          <t>91624</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>188014</t>
+          <t>96572</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>196401</t>
+          <t>100010</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>208537</t>
+          <t>108708</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>221235</t>
+          <t>112709</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>234366</t>
+          <t>121839</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>245906</t>
+          <t>124249</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>248830</t>
+          <t>124763</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>249147</t>
+          <t>124566</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>247716</t>
+          <t>123331</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>245896</t>
+          <t>122746</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>240596</t>
+          <t>118031</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>231029</t>
+          <t>113179</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>226177</t>
+          <t>113179</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
